--- a/artfynd/A 29675-2025 artfynd.xlsx
+++ b/artfynd/A 29675-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126405552</v>
+        <v>126405548</v>
       </c>
       <c r="B2" t="n">
-        <v>75011</v>
+        <v>5176</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6426</v>
+        <v>100526</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Stora Tingvallamossen, Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>328988</v>
+        <v>329270</v>
       </c>
       <c r="R2" t="n">
-        <v>6525856</v>
+        <v>6525899</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -787,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126405548</v>
+        <v>126405552</v>
       </c>
       <c r="B3" t="n">
-        <v>5176</v>
+        <v>75011</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,39 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100526</v>
+        <v>6426</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stora Tingvallamossen, Dls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>329270</v>
+        <v>328988</v>
       </c>
       <c r="R3" t="n">
-        <v>6525899</v>
+        <v>6525856</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>

--- a/artfynd/A 29675-2025 artfynd.xlsx
+++ b/artfynd/A 29675-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126405548</v>
+        <v>126405552</v>
       </c>
       <c r="B2" t="n">
-        <v>5176</v>
+        <v>75014</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100526</v>
+        <v>6426</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Stora Tingvallamossen, Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>329270</v>
+        <v>328988</v>
       </c>
       <c r="R2" t="n">
-        <v>6525899</v>
+        <v>6525856</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -792,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126405552</v>
+        <v>126405548</v>
       </c>
       <c r="B3" t="n">
-        <v>75011</v>
+        <v>5176</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,34 +798,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6426</v>
+        <v>100526</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stora Tingvallamossen, Dls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>328988</v>
+        <v>329270</v>
       </c>
       <c r="R3" t="n">
-        <v>6525856</v>
+        <v>6525899</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
